--- a/tongcheng-bim/out/02_ตารางโครงสร้าง_ฐานราก_เสา_คาน.xlsx
+++ b/tongcheng-bim/out/02_ตารางโครงสร้าง_ฐานราก_เสา_คาน.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-เสา เหล็กเสริม" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-คาน รายช่วง" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-คาน เหล็กเสริม" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-ข้อมูลที่ต้องยืนยัน" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-รอยต่อเสาเหล็ก" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-ข้อมูลที่ต้องยืนยัน" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76407,7 +76408,3236 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:P51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>รอยต่อเสาเหล็ก H244x175 กับหัวเสา คสล.: แผ่นเหล็กฐาน PL20x200x450 + Anchor bolt M20x750 6 ชุด + แผ่นหัวเสา PL20x200x450 (แบบขยาย D01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>งานก่อสร้างอาคารโกดังและงานบริเวณ บริษัท ตงเฉิน อีเล็คทริค เคเบิ้ล แอนด์ไวร์ จำกัด | WEC-TC-6901</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>รหัสเสาเหล็ก</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>ตำแหน่งกริด</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>เสา คสล. ใต้</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>ด้านยาวแผ่นตามแนว</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Base plate (มม.)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Base plate (กก.)</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Top plate (มม.)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Top plate (กก.)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Anchor bolt (ชุด)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Anchor bolt (กก.)</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>ระยะฝังสลัก (ม.)</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>เกราท์ (ลบ.ม.)</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>ระยะหุ้มเหล็กยืนเสา (ม.)</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>ระยะสลัก-เหล็กมุมเสา ศก. (มม.)</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ระยะช่องว่าง (มม.)</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>ผล</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>SC1-001</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>1/A</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>C1-001</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M4" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N4" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O4" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N4-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P4" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O4&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>SC1-002</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2/A</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>C1-002</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M5" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N5" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O5" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N5-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P5" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O5&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>SC1-003</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>3/A</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>C1-003</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M6" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N6" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O6" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N6-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P6" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O6&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>SC1-004</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>4/A</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>C1-004</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M7" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N7" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O7" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N7-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P7" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O7&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>SC1-005</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>5/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>C1-005</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M8" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N8" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O8" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N8-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P8" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O8&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>SC1-006</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>6/A</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>C1-006</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M9" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N9" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O9" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N9-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P9" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O9&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>SC1-007</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>7/A</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>C1-007</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M10" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N10" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O10" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N10-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P10" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O10&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>SC1-008</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>8/A</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>C1-008</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M11" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N11" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O11" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N11-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P11" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O11&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>SC1-009</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>9/A</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>C1-009</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M12" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N12" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O12" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N12-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P12" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O12&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>SC1-010</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>10/A</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>C1-010</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M13" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N13" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O13" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N13-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P13" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O13&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>SC1-011</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>11/A</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>C1-011</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M14" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N14" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O14" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N14-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P14" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O14&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>SC1-012</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>1/B</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>C1-012</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M15" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N15" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O15" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N15-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P15" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O15&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>SC1-013</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>6/B</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>C1-013</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M16" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N16" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O16" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N16-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P16" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O16&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>SC1-014</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>11/B</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>C1-014</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M17" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N17" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O17" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N17-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P17" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O17&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>SC1-015</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>1/C</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>C1-015</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M18" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N18" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O18" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N18-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P18" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O18&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>SC1-016</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>6/C</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>C1-016</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M19" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N19" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O19" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N19-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P19" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O19&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>SC1-017</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>11/C</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>C1-017</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M20" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N20" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O20" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N20-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P20" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O20&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>SC1-018</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>C1-018</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M21" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N21" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O21" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N21-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P21" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O21&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>SC1-019</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>6/D</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>C1-019</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M22" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N22" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O22" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N22-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P22" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O22&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>SC1-020</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>11/D</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>C1-020</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M23" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N23" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O23" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N23-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P23" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O23&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>SC1-021</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>1/E</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>C1-021</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M24" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N24" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O24" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N24-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P24" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O24&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>SC1-022</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>6/E</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>C1-022</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M25" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N25" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O25" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N25-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P25" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O25&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>SC1-023</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>11/E</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>C1-023</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M26" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N26" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O26" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N26-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P26" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O26&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>SC1-024</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>1/F</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>C1-024</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M27" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N27" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O27" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N27-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P27" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O27&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>SC1-025</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>6/F</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>C1-025</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M28" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N28" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O28" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N28-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P28" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O28&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>SC1-026</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>11/F</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>C1-026</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M29" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N29" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O29" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N29-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P29" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O29&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>SC1-027</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>1/G</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>C1-027</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M30" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N30" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O30" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N30-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P30" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O30&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>SC1-028</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>6/G</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>C1-028</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M31" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N31" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O31" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N31-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P31" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O31&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>SC1-029</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>11/G</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>C1-029</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M32" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N32" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O32" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N32-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P32" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O32&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>SC1-030</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>1/H</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>C1-030</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M33" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N33" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O33" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N33-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P33" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O33&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>SC1-031</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>6/H</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>C1-031</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M34" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N34" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O34" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N34-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P34" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O34&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>SC1-032</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>11/H</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>C1-032</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M35" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N35" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O35" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N35-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P35" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O35&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>SC1-033</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>1/I</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>C1-033</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M36" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N36" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O36" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N36-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P36" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O36&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>SC1-034</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>6/I</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>C1-034</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M37" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N37" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O37" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N37-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P37" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O37&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>SC1-035</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>11/I</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>C1-035</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M38" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N38" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O38" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N38-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P38" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O38&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>SC1-036</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>1/J</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>C1-036</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M39" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N39" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O39" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N39-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P39" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O39&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>SC1-037</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>2/J</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>C1-037</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L40" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M40" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N40" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O40" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N40-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P40" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O40&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>SC1-038</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>3/J</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>C1-038</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M41" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N41" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.15000000000000036-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O41" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N41-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P41" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O41&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>SC1-039</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>4/J</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>C1-039</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L42" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M42" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N42" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O42" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N42-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P42" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O42&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>SC1-040</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>5/J</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>C1-040</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M43" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N43" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O43" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N43-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P43" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O43&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>SC1-041</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>6/J</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>C2-001</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M44" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N44" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O44" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N44-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P44" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C2",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O44&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>SC1-042</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>7/J</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>C1-041</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M45" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N45" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O45" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N45-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P45" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O45&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>SC1-043</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>8/J</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>C1-042</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M46" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N46" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O46" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N46-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P46" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O46&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>SC1-044</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>9/J</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>C1-043</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M47" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N47" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O47" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N47-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P47" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O47&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>SC1-045</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>10/J</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>C1-044</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M48" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N48" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O48" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N48-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P48" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O48&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>SC1-046</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>11/J</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>C1-045</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>20x200x450</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="M49" s="8">
+        <f>INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="N49" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(1000*SQRT((0.25-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.175)^2+(0.14999999999999858-INDEX('4-เสา เหล็กเสริม'!$E:$E,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))-INDEX('4-เสา เหล็กเสริม'!$J:$J,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/1000-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2000-0.05)^2),1))</f>
+        <v/>
+      </c>
+      <c r="O49" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",ROUND(N49-10.0-INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))/2,1))</f>
+        <v/>
+      </c>
+      <c r="P49" s="8">
+        <f>IF(INDEX('4-เสา เหล็กเสริม'!$G:$G,MATCH("C1",'4-เสา เหล็กเสริม'!$A:$A,0))=0,"รอตารางเสา",IF(O49&gt;=25,"ผ่าน (≥25 มม.)","ชน/แคบ ตรวจแบบ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>รวม</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr"/>
+      <c r="C50" s="8" t="inlineStr"/>
+      <c r="D50" s="8" t="inlineStr"/>
+      <c r="E50" s="8">
+        <f>COUNTA(E4:E49)</f>
+        <v/>
+      </c>
+      <c r="F50" s="8">
+        <f>SUM(F4:F49)</f>
+        <v/>
+      </c>
+      <c r="G50" s="8">
+        <f>COUNTA(G4:G49)</f>
+        <v/>
+      </c>
+      <c r="H50" s="8">
+        <f>SUM(H4:H49)</f>
+        <v/>
+      </c>
+      <c r="I50" s="8">
+        <f>SUM(I4:I49)</f>
+        <v/>
+      </c>
+      <c r="J50" s="8">
+        <f>SUM(J4:J49)</f>
+        <v/>
+      </c>
+      <c r="K50" s="8" t="inlineStr"/>
+      <c r="L50" s="8">
+        <f>SUM(L4:L49)</f>
+        <v/>
+      </c>
+      <c r="M50" s="8" t="n"/>
+      <c r="N50" s="8" t="n"/>
+      <c r="O50" s="8" t="n"/>
+      <c r="P50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>หมายเหตุ: ค่าเบื้องต้นจากผู้ว่าจ้าง 28/10/69; ตำแหน่งสลัก 3x2 ระยะ 175x100 มม. ระยะขอบแผ่น 50 มม. (สมมติ) ฝังจากหัวเสา +4.50 ลึก 645 มม.; การตรวจระยะใช้เหล็กยืนมุมเสา (ระยะหุ้ม + ปลอก + Ø/2) จากชีต 4 เกณฑ์ช่องว่าง ≥ 25 มม.; สลักคู่กลางอยู่ระหว่างปีกเสา H ตรวจที่ขันน็อต</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
+      <c r="N51" s="8" t="n"/>
+      <c r="O51" s="8" t="n"/>
+      <c r="P51" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -76643,27 +79873,27 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>แท่นหม้อแปลง (A104)</t>
+          <t>รอยต่อเสาเหล็ก-หัวเสา (D01)</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>จำนวนและตำแหน่งเข็มไม่ตรงกัน</t>
+          <t>ระยะ/ตำแหน่งสลัก การต่อแผ่นหัวเสากับโครงถัก</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>A104 แสดงเข็ม 3x3 = 9 ต้น ระยะ 2.10 x 1.10 ม.; S201/S201-B แสดง I22-TR 6 ต้น ระยะ ~1.50 ม.</t>
+          <t>ผู้ว่าจ้างกำหนด PL20x200x450 + M20x750 6 ชุด; ตำแหน่งสลักสมมติ 175x100 มม.</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>ยืนยันจำนวน/ตำแหน่งเข็ม และระดับแท่น</t>
+          <t>ยืนยันระยะสลัก ระยะขอบ ขนาดรู และสลักยึดโครงถัก</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>4.3.1 (+3 ต้นถ้าใช้ A104)</t>
+          <t>2.5.7-2.5.9</t>
         </is>
       </c>
     </row>
@@ -76673,27 +79903,27 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>ห้องเก็บสารเคมี (A103)</t>
+          <t>แท่นหม้อแปลง (A104)</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>ระดับพื้นและตำแหน่งเสา</t>
+          <t>จำนวนและตำแหน่งเข็มไม่ตรงกัน</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>A103 พื้น +0.40 มีเสากลางผนังที่ y=3.0 ม.; S201 มี F1P-1 ที่ y=0, 6.0, 9.0 (ไม่มีที่ y=3.0); S6.1 AF01 ระดับถนน</t>
+          <t>A104 แสดงเข็ม 3x3 = 9 ต้น ระยะ 2.10 x 1.10 ม.; S201/S201-B แสดง I22-TR 6 ต้น ระยะ ~1.50 ม.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>ยืนยันตำแหน่งฐาน/เสา และระดับพื้น</t>
+          <t>ยืนยันจำนวน/ตำแหน่งเข็ม และระดับแท่น</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>2.2.3 / 2.3.3 / 2.4.2</t>
+          <t>4.3.1 (+3 ต้นถ้าใช้ A104)</t>
         </is>
       </c>
     </row>
@@ -76703,27 +79933,27 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>เข็มถนน I22</t>
+          <t>ห้องเก็บสารเคมี (A103)</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>ตำแหน่งที่ขาด 17 ต้น</t>
+          <t>ระดับพื้นและตำแหน่งเสา</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>ตาราง S2 = 249, ผัง S201/S202 = 232</t>
+          <t>A103 พื้น +0.40 มีเสากลางผนังที่ y=3.0 ม.; S201 มี F1P-1 ที่ y=0, 6.0, 9.0 (ไม่มีที่ y=3.0); S6.1 AF01 ระดับถนน</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>ตำแหน่งเข็ม 17 ต้น</t>
+          <t>ยืนยันตำแหน่งฐาน/เสา และระดับพื้น</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>4.1.1 / 4.1.2 (ใช้ 249 แล้ว)</t>
+          <t>2.2.3 / 2.3.3 / 2.4.2</t>
         </is>
       </c>
     </row>
@@ -76733,27 +79963,27 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>ฐาน 0.66 ม. แนวเขต 16 จุด</t>
+          <t>เข็มถนน I22</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>หน้าที่และระดับ</t>
+          <t>ตำแหน่งที่ขาด 17 ต้น</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>พบในผัง S201 ไม่มีในตาราง</t>
+          <t>ตาราง S2 = 249, ผัง S201/S202 = 232</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>ระบุว่าเป็นฐานอะไร (รั้ว/เสาไฟ/ป้าย) และขนาดความลึก</t>
+          <t>ตำแหน่งเข็ม 17 ต้น</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>4.6.1</t>
+          <t>4.1.1 / 4.1.2 (ใช้ 249 แล้ว)</t>
         </is>
       </c>
     </row>
@@ -76763,25 +79993,55 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
+          <t>ฐาน 0.66 ม. แนวเขต 16 จุด</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>หน้าที่และระดับ</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>พบในผัง S201 ไม่มีในตาราง</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>ระบุว่าเป็นฐานอะไร (รั้ว/เสาไฟ/ป้าย) และขนาดความลึก</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>4.6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>ถังเก็บน้ำใต้ดิน</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>ผนัง ฝา เหล็กเสริม</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>S202 แสดงเฉพาะพื้น TF -2.60 / BF -2.85</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>แบบขยายถัง</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>4.4.3 / 4.4.4</t>
         </is>
